--- a/data/trans_dic/P21D_6_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,01</t>
+          <t>0,22; 1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,3</t>
+          <t>0,21; 1,96</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,68</t>
+          <t>0,32; 1,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,19</t>
+          <t>0,2; 1,16</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,14</t>
+          <t>0,37; 2,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,52</t>
+          <t>0,3; 1,51</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,94</t>
+          <t>0,14; 1,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,83</t>
+          <t>1,08; 3,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,37</t>
+          <t>0,86; 2,38</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,08</t>
+          <t>0,22; 1,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,82</t>
+          <t>0,85; 1,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,24</t>
+          <t>0,59; 1,22</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 9688</t>
+          <t>0; 9708</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>594; 6000</t>
+          <t>670; 5750</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1281; 12994</t>
+          <t>1210; 11101</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8233</t>
+          <t>0; 9158</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1526; 7496</t>
+          <t>1427; 7414</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2052; 13155</t>
+          <t>2216; 12834</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7526</t>
+          <t>0; 6311</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1064; 7042</t>
+          <t>1209; 6770</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2123; 10039</t>
+          <t>1984; 9917</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>563; 7926</t>
+          <t>569; 7726</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6183; 19827</t>
+          <t>5611; 19105</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8180; 21983</t>
+          <t>7968; 22060</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3352; 17969</t>
+          <t>3735; 17563</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13392; 29039</t>
+          <t>13469; 29134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19536; 40407</t>
+          <t>19316; 39603</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_6_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,92</t>
+          <t>0,21; 1,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,96</t>
+          <t>0,23; 2,02</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,66</t>
+          <t>0,37; 1,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,16</t>
+          <t>0,32; 1,26</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,06</t>
+          <t>0,29; 1,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,51</t>
+          <t>0,31; 1,41</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,89</t>
+          <t>0,13; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,69</t>
+          <t>1,34; 3,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,38</t>
+          <t>0,96; 2,42</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,06</t>
+          <t>0,25; 1,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,83</t>
+          <t>0,83; 1,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,22</t>
+          <t>0,66; 1,26</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4234</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 9708</t>
+          <t>0; 9524</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>670; 5750</t>
+          <t>664; 5955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1210; 11101</t>
+          <t>1383; 12368</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6447</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9158</t>
+          <t>0; 7037</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1427; 7414</t>
+          <t>1876; 8675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2216; 12834</t>
+          <t>3096; 12280</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5058</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6311</t>
+          <t>0; 6620</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1209; 6770</t>
+          <t>1093; 6530</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1984; 9917</t>
+          <t>2359; 10607</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>13822</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>569; 7726</t>
+          <t>576; 7832</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5611; 19105</t>
+          <t>6592; 17805</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7968; 22060</t>
+          <t>8831; 22319</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3735; 17563</t>
+          <t>3935; 17198</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13469; 29134</t>
+          <t>14057; 29193</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19316; 39603</t>
+          <t>21586; 40987</t>
         </is>
       </c>
     </row>
